--- a/dados/excel/genero_por_categoria.xlsx
+++ b/dados/excel/genero_por_categoria.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$H$16</definedName>
@@ -640,7 +640,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10/10/2026 14:55</t>
+          <t>12/10/2026 16:30</t>
         </is>
       </c>
     </row>

--- a/dados/excel/genero_por_categoria.xlsx
+++ b/dados/excel/genero_por_categoria.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026 16:30</t>
+          <t>16/10/2026 19:58</t>
         </is>
       </c>
     </row>
@@ -886,16 +886,16 @@
         </is>
       </c>
       <c r="C2" s="9" t="n">
-        <v>5455</v>
+        <v>5453</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>82258231.34</v>
+        <v>82226720.32000001</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>15079.41912740605</v>
+        <v>15079.1711571612</v>
       </c>
       <c r="G2" s="11" t="n">
         <v>621</v>
@@ -946,16 +946,16 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>1867276.81</v>
+        <v>1898787.83</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>14254.02145038168</v>
+        <v>14276.60022556391</v>
       </c>
       <c r="G4" s="11" t="n">
         <v>621</v>
@@ -976,22 +976,22 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>479186</v>
+        <v>476636</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>10149</v>
+        <v>10091</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>3527338956.9</v>
+        <v>3508583559.26</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>7361.106035860814</v>
+        <v>7361.138393365168</v>
       </c>
       <c r="G5" s="16" t="n">
         <v>13740</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>73.86</v>
+        <v>73.44</v>
       </c>
     </row>
     <row r="6">
@@ -1006,22 +1006,22 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>155305</v>
+        <v>154340</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>3404</v>
+        <v>3380</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1432945406.78</v>
+        <v>1424477043.68</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>9226.653403174398</v>
+        <v>9229.474171828431</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>13740</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>73.86</v>
+        <v>73.44</v>
       </c>
     </row>
     <row r="7">
@@ -1036,22 +1036,22 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>9025</v>
+        <v>12540</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>187</v>
+        <v>269</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>69834495.31999999</v>
+        <v>97058256.06</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>7737.894218282548</v>
+        <v>7739.892827751196</v>
       </c>
       <c r="G7" s="16" t="n">
         <v>13740</v>
       </c>
       <c r="H7" s="17" t="n">
-        <v>73.86</v>
+        <v>73.44</v>
       </c>
     </row>
     <row r="8">
@@ -1066,22 +1066,22 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>139810</v>
+        <v>139133</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>10292</v>
+        <v>10238</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>221420896.11</v>
+        <v>220390128.72</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1583.727173378156</v>
+        <v>1584.024844716926</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>11925</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>86.31</v>
+        <v>85.84999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1096,22 +1096,22 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>16051</v>
+        <v>15770</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1519</v>
+        <v>1498</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>35257936.64</v>
+        <v>34820231.43</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>2196.619315930472</v>
+        <v>2208.004529486367</v>
       </c>
       <c r="G9" s="16" t="n">
         <v>11925</v>
       </c>
       <c r="H9" s="17" t="n">
-        <v>86.31</v>
+        <v>85.84999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1126,22 +1126,22 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1595</v>
+        <v>2553</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>114</v>
+        <v>189</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3547081.88</v>
+        <v>5015554.48</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2223.875786833856</v>
+        <v>1964.572847630239</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>11925</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>86.31</v>
+        <v>85.84999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1156,22 +1156,22 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>26028</v>
+        <v>25942</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>303260106.29</v>
+        <v>302324227.78</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>11651.30268518519</v>
+        <v>11653.85196900778</v>
       </c>
       <c r="G11" s="16" t="n">
         <v>962</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>63.41</v>
+        <v>62.99</v>
       </c>
     </row>
     <row r="12">
@@ -1186,22 +1186,22 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>14260</v>
+        <v>14118</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>181707478.03</v>
+        <v>179802302.72</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>12742.45988990182</v>
+        <v>12735.6780507154</v>
       </c>
       <c r="G12" s="11" t="n">
         <v>962</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>63.41</v>
+        <v>62.99</v>
       </c>
     </row>
     <row r="13">
@@ -1216,22 +1216,22 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>479</v>
+        <v>707</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>8061006.24</v>
+        <v>10902060.06</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>16828.8230480167</v>
+        <v>15420.16981612447</v>
       </c>
       <c r="G13" s="16" t="n">
         <v>962</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>63.41</v>
+        <v>62.99</v>
       </c>
     </row>
     <row r="14">
@@ -1246,22 +1246,22 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>10816</v>
+        <v>10602</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>46491210.45</v>
+        <v>45288513.87</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>4298.373747226332</v>
+        <v>4271.695328239955</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>298</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>68.79000000000001</v>
+        <v>67.45</v>
       </c>
     </row>
     <row r="15">
@@ -1291,7 +1291,7 @@
         <v>298</v>
       </c>
       <c r="H15" s="17" t="n">
-        <v>68.79000000000001</v>
+        <v>67.45</v>
       </c>
     </row>
     <row r="16">
@@ -1306,22 +1306,22 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>204</v>
+        <v>418</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1292840.97</v>
+        <v>2495537.55</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>6337.455735294117</v>
+        <v>5970.185526315789</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>298</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>68.79000000000001</v>
+        <v>67.45</v>
       </c>
     </row>
   </sheetData>
